--- a/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP186"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.88</v>
@@ -1786,7 +1786,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.11</v>
@@ -2440,7 +2440,7 @@
         <v>0.11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
         <v>1.38</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.67</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.78</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.11</v>
@@ -6800,7 +6800,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR29" t="n">
         <v>1.62</v>
@@ -7236,7 +7236,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR31" t="n">
         <v>1.47</v>
@@ -7672,7 +7672,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR33" t="n">
         <v>1.01</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.44</v>
@@ -9634,7 +9634,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR42" t="n">
         <v>1.98</v>
@@ -10288,7 +10288,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR45" t="n">
         <v>1.29</v>
@@ -10503,7 +10503,7 @@
         <v>1</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.89</v>
@@ -10721,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.88</v>
@@ -10942,7 +10942,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR48" t="n">
         <v>1.09</v>
@@ -11593,7 +11593,7 @@
         <v>3</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ51" t="n">
         <v>2</v>
@@ -12686,7 +12686,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR56" t="n">
         <v>1.29</v>
@@ -13337,7 +13337,7 @@
         <v>3</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.38</v>
@@ -14645,7 +14645,7 @@
         <v>2</v>
       </c>
       <c r="AP65" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ65" t="n">
         <v>2</v>
@@ -15302,7 +15302,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR68" t="n">
         <v>2.16</v>
@@ -15517,7 +15517,7 @@
         <v>1.67</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ69" t="n">
         <v>0.78</v>
@@ -15738,7 +15738,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR70" t="n">
         <v>1.62</v>
@@ -15953,10 +15953,10 @@
         <v>2</v>
       </c>
       <c r="AP71" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR71" t="n">
         <v>1.3</v>
@@ -17046,7 +17046,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR76" t="n">
         <v>1.58</v>
@@ -17261,7 +17261,7 @@
         <v>0.67</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.3</v>
@@ -18136,7 +18136,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR81" t="n">
         <v>1.17</v>
@@ -19223,7 +19223,7 @@
         <v>1.33</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.11</v>
@@ -19659,7 +19659,7 @@
         <v>1.33</v>
       </c>
       <c r="AP88" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ88" t="n">
         <v>1.78</v>
@@ -19880,7 +19880,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR89" t="n">
         <v>1.27</v>
@@ -20095,7 +20095,7 @@
         <v>2.25</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ90" t="n">
         <v>2</v>
@@ -20967,10 +20967,10 @@
         <v>1.25</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR94" t="n">
         <v>1.22</v>
@@ -21624,7 +21624,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR97" t="n">
         <v>1.09</v>
@@ -21842,7 +21842,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR98" t="n">
         <v>1.07</v>
@@ -22275,7 +22275,7 @@
         <v>1.5</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.38</v>
@@ -23147,10 +23147,10 @@
         <v>1</v>
       </c>
       <c r="AP104" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR104" t="n">
         <v>0.97</v>
@@ -24019,7 +24019,7 @@
         <v>1</v>
       </c>
       <c r="AP108" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ108" t="n">
         <v>0.78</v>
@@ -24894,7 +24894,7 @@
         <v>0.11</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR112" t="n">
         <v>1.16</v>
@@ -25327,10 +25327,10 @@
         <v>1</v>
       </c>
       <c r="AP114" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR114" t="n">
         <v>1.24</v>
@@ -25548,7 +25548,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR115" t="n">
         <v>1.52</v>
@@ -26635,7 +26635,7 @@
         <v>1.33</v>
       </c>
       <c r="AP120" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.33</v>
@@ -27725,7 +27725,7 @@
         <v>1.6</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.38</v>
@@ -27943,10 +27943,10 @@
         <v>0.8</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR126" t="n">
         <v>1.21</v>
@@ -28600,7 +28600,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR129" t="n">
         <v>1.12</v>
@@ -28815,7 +28815,7 @@
         <v>1.17</v>
       </c>
       <c r="AP130" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ130" t="n">
         <v>1</v>
@@ -29254,7 +29254,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR132" t="n">
         <v>1.18</v>
@@ -29472,7 +29472,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR133" t="n">
         <v>1.15</v>
@@ -29690,7 +29690,7 @@
         <v>0.11</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR134" t="n">
         <v>1.2</v>
@@ -31213,7 +31213,7 @@
         <v>1.14</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ141" t="n">
         <v>0.89</v>
@@ -31431,7 +31431,7 @@
         <v>0.86</v>
       </c>
       <c r="AP142" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.3</v>
@@ -31649,7 +31649,7 @@
         <v>1.83</v>
       </c>
       <c r="AP143" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.67</v>
@@ -32088,7 +32088,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR145" t="n">
         <v>1.84</v>
@@ -32306,7 +32306,7 @@
         <v>2</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR146" t="n">
         <v>1.36</v>
@@ -33178,7 +33178,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR150" t="n">
         <v>1.12</v>
@@ -33614,7 +33614,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR152" t="n">
         <v>1.23</v>
@@ -34919,7 +34919,7 @@
         <v>1.13</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ158" t="n">
         <v>1.3</v>
@@ -35573,7 +35573,7 @@
         <v>0.57</v>
       </c>
       <c r="AP161" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ161" t="n">
         <v>0.78</v>
@@ -36009,7 +36009,7 @@
         <v>0.43</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.44</v>
@@ -37971,10 +37971,10 @@
         <v>1.88</v>
       </c>
       <c r="AP172" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AR172" t="n">
         <v>1.76</v>
@@ -38192,7 +38192,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR173" t="n">
         <v>1.86</v>
@@ -38410,7 +38410,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AR174" t="n">
         <v>1.66</v>
@@ -38625,7 +38625,7 @@
         <v>1.5</v>
       </c>
       <c r="AP175" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.67</v>
@@ -38846,7 +38846,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR176" t="n">
         <v>1.04</v>
@@ -41102,6 +41102,878 @@
       </c>
       <c r="BP186" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>8042770</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>46081.6875</v>
+      </c>
+      <c r="F187" t="n">
+        <v>20</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>El Geish</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>1</v>
+      </c>
+      <c r="L187" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>1</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R187" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S187" t="n">
+        <v>7</v>
+      </c>
+      <c r="T187" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U187" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="V187" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="W187" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X187" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ187" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU187" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB187" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC187" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF187" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG187" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BH187" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BI187" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BJ187" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BK187" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BL187" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM187" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BN187" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BO187" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BP187" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>8042771</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>46081.6875</v>
+      </c>
+      <c r="F188" t="n">
+        <v>20</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Ismaily SC</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>El Gounah</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="n">
+        <v>2</v>
+      </c>
+      <c r="N188" t="n">
+        <v>3</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>['88', '90+4']</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R188" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S188" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T188" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U188" t="n">
+        <v>2</v>
+      </c>
+      <c r="V188" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W188" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X188" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB188" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF188" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BG188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BI188" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BJ188" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BK188" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BL188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM188" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BN188" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BO188" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="BP188" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>8042772</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>46081.6875</v>
+      </c>
+      <c r="F189" t="n">
+        <v>20</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Al Ahly</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Masr</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" t="n">
+        <v>1</v>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>1</v>
+      </c>
+      <c r="N189" t="n">
+        <v>2</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R189" t="n">
+        <v>2</v>
+      </c>
+      <c r="S189" t="n">
+        <v>6</v>
+      </c>
+      <c r="T189" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U189" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V189" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="W189" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X189" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF189" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG189" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BI189" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK189" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BL189" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BM189" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN189" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO189" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BP189" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>8042778</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>46081.6875</v>
+      </c>
+      <c r="F190" t="n">
+        <v>20</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Wadi Degla</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="n">
+        <v>1</v>
+      </c>
+      <c r="N190" t="n">
+        <v>2</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>4</v>
+      </c>
+      <c r="R190" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S190" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T190" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U190" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V190" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="W190" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X190" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BK190" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BL190" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BM190" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BN190" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO190" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BP190" t="n">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.75</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ10" t="n">
         <v>1</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.38</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.44</v>
@@ -3748,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.67</v>
@@ -4838,7 +4838,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ22" t="n">
         <v>0.78</v>
@@ -5489,10 +5489,10 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR23" t="n">
         <v>1.28</v>
@@ -6364,7 +6364,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR27" t="n">
         <v>1.07</v>
@@ -6582,7 +6582,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR28" t="n">
         <v>0</v>
@@ -7015,10 +7015,10 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR30" t="n">
         <v>0.8</v>
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.78</v>
@@ -7669,7 +7669,7 @@
         <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.8</v>
@@ -8759,7 +8759,7 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.38</v>
@@ -8980,7 +8980,7 @@
         <v>0.11</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR39" t="n">
         <v>1.08</v>
@@ -9198,7 +9198,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR40" t="n">
         <v>1.15</v>
@@ -9849,7 +9849,7 @@
         <v>2</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ43" t="n">
         <v>0.78</v>
@@ -10067,7 +10067,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ44" t="n">
         <v>1</v>
@@ -10506,7 +10506,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR46" t="n">
         <v>1.03</v>
@@ -10939,7 +10939,7 @@
         <v>1</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.5</v>
@@ -11160,7 +11160,7 @@
         <v>2</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR49" t="n">
         <v>1.22</v>
@@ -11378,7 +11378,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR50" t="n">
         <v>1.62</v>
@@ -11596,7 +11596,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ51" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR51" t="n">
         <v>1.25</v>
@@ -12247,7 +12247,7 @@
         <v>1.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.78</v>
@@ -12904,7 +12904,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR57" t="n">
         <v>0.9399999999999999</v>
@@ -13122,7 +13122,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR58" t="n">
         <v>1.64</v>
@@ -13773,7 +13773,7 @@
         <v>1</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.75</v>
@@ -14212,7 +14212,7 @@
         <v>2</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR63" t="n">
         <v>1.39</v>
@@ -14430,7 +14430,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR64" t="n">
         <v>1.15</v>
@@ -14648,7 +14648,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ65" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR65" t="n">
         <v>1.03</v>
@@ -14863,7 +14863,7 @@
         <v>1.33</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ66" t="n">
         <v>1</v>
@@ -15081,10 +15081,10 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR67" t="n">
         <v>1.17</v>
@@ -15299,7 +15299,7 @@
         <v>1.67</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ68" t="n">
         <v>1.4</v>
@@ -16171,10 +16171,10 @@
         <v>1.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR72" t="n">
         <v>1.04</v>
@@ -16610,7 +16610,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR74" t="n">
         <v>1.41</v>
@@ -17479,7 +17479,7 @@
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ78" t="n">
         <v>0.44</v>
@@ -17915,7 +17915,7 @@
         <v>2</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.67</v>
@@ -18354,7 +18354,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR82" t="n">
         <v>1.66</v>
@@ -18569,7 +18569,7 @@
         <v>1.25</v>
       </c>
       <c r="AP83" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ83" t="n">
         <v>0.78</v>
@@ -18790,7 +18790,7 @@
         <v>2</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR84" t="n">
         <v>1.44</v>
@@ -19005,7 +19005,7 @@
         <v>0.33</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ85" t="n">
         <v>0.67</v>
@@ -19226,7 +19226,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR86" t="n">
         <v>1.24</v>
@@ -20098,7 +20098,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ90" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR90" t="n">
         <v>1.55</v>
@@ -20531,7 +20531,7 @@
         <v>0.75</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ92" t="n">
         <v>1.3</v>
@@ -20749,10 +20749,10 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR93" t="n">
         <v>1.71</v>
@@ -21188,7 +21188,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR95" t="n">
         <v>1.7</v>
@@ -21839,7 +21839,7 @@
         <v>1.25</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.4</v>
@@ -22057,7 +22057,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.67</v>
@@ -22496,7 +22496,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR101" t="n">
         <v>1.07</v>
@@ -23368,7 +23368,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR105" t="n">
         <v>1.37</v>
@@ -23801,7 +23801,7 @@
         <v>0.5</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.67</v>
@@ -24240,7 +24240,7 @@
         <v>2</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR109" t="n">
         <v>1.5</v>
@@ -24458,7 +24458,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR110" t="n">
         <v>1.09</v>
@@ -24673,7 +24673,7 @@
         <v>0.6</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.3</v>
@@ -25109,7 +25109,7 @@
         <v>0.6</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ113" t="n">
         <v>0.44</v>
@@ -25763,7 +25763,7 @@
         <v>1.6</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.67</v>
@@ -26199,10 +26199,10 @@
         <v>1.8</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ118" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR118" t="n">
         <v>1.69</v>
@@ -26638,7 +26638,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR120" t="n">
         <v>1.03</v>
@@ -27289,7 +27289,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.78</v>
@@ -27510,7 +27510,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR124" t="n">
         <v>1.17</v>
@@ -27728,7 +27728,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR125" t="n">
         <v>1.66</v>
@@ -28164,7 +28164,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR127" t="n">
         <v>1.52</v>
@@ -28597,7 +28597,7 @@
         <v>1.83</v>
       </c>
       <c r="AP129" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ129" t="n">
         <v>1.5</v>
@@ -29033,7 +29033,7 @@
         <v>1.83</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.78</v>
@@ -29251,7 +29251,7 @@
         <v>1.83</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.8</v>
@@ -29905,7 +29905,7 @@
         <v>1</v>
       </c>
       <c r="AP135" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.3</v>
@@ -30998,7 +30998,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR140" t="n">
         <v>1.18</v>
@@ -31216,7 +31216,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ141" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR141" t="n">
         <v>1.3</v>
@@ -31870,7 +31870,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR144" t="n">
         <v>1.71</v>
@@ -32085,7 +32085,7 @@
         <v>2</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ145" t="n">
         <v>1.8</v>
@@ -32521,10 +32521,10 @@
         <v>1.17</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR147" t="n">
         <v>1.17</v>
@@ -32957,7 +32957,7 @@
         <v>0.5</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.44</v>
@@ -33175,7 +33175,7 @@
         <v>1.29</v>
       </c>
       <c r="AP150" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ150" t="n">
         <v>1.4</v>
@@ -33611,7 +33611,7 @@
         <v>0.71</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.5</v>
@@ -33829,7 +33829,7 @@
         <v>1.67</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.75</v>
@@ -34268,7 +34268,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR155" t="n">
         <v>1.41</v>
@@ -34486,7 +34486,7 @@
         <v>0.11</v>
       </c>
       <c r="AQ156" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR156" t="n">
         <v>1.14</v>
@@ -35140,7 +35140,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR159" t="n">
         <v>1.3</v>
@@ -36227,7 +36227,7 @@
         <v>1.5</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.88</v>
@@ -36448,7 +36448,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR165" t="n">
         <v>1.67</v>
@@ -36881,10 +36881,10 @@
         <v>1.38</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR167" t="n">
         <v>1.28</v>
@@ -37099,10 +37099,10 @@
         <v>1.25</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR168" t="n">
         <v>1.29</v>
@@ -37317,7 +37317,7 @@
         <v>1.88</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.78</v>
@@ -37538,7 +37538,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR170" t="n">
         <v>1.4</v>
@@ -37753,10 +37753,10 @@
         <v>1.13</v>
       </c>
       <c r="AP171" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AR171" t="n">
         <v>1.15</v>
@@ -38189,7 +38189,7 @@
         <v>1.75</v>
       </c>
       <c r="AP173" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AQ173" t="n">
         <v>1.5</v>
@@ -40372,7 +40372,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ183" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AR183" t="n">
         <v>1.31</v>
@@ -40587,7 +40587,7 @@
         <v>0.75</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.67</v>
@@ -41477,7 +41477,7 @@
         <v>2</v>
       </c>
       <c r="AV188" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW188" t="n">
         <v>4</v>
@@ -41489,7 +41489,7 @@
         <v>6</v>
       </c>
       <c r="AZ188" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA188" t="n">
         <v>1</v>
@@ -41973,6 +41973,1314 @@
         <v>4.17</v>
       </c>
       <c r="BP190" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>8042775</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>46082.6875</v>
+      </c>
+      <c r="F191" t="n">
+        <v>20</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>ENPPI</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Al Masry</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>1</v>
+      </c>
+      <c r="J191" t="n">
+        <v>2</v>
+      </c>
+      <c r="K191" t="n">
+        <v>3</v>
+      </c>
+      <c r="L191" t="n">
+        <v>3</v>
+      </c>
+      <c r="M191" t="n">
+        <v>2</v>
+      </c>
+      <c r="N191" t="n">
+        <v>5</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>['34', '53', '90+14']</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>['17', '43']</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>4</v>
+      </c>
+      <c r="R191" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S191" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U191" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="V191" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W191" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X191" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="n">
+        <v>8042773</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>46082.6875</v>
+      </c>
+      <c r="F192" t="n">
+        <v>20</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Petrojet</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>1</v>
+      </c>
+      <c r="L192" t="n">
+        <v>1</v>
+      </c>
+      <c r="M192" t="n">
+        <v>1</v>
+      </c>
+      <c r="N192" t="n">
+        <v>2</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>['90+5']</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R192" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S192" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T192" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="V192" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="W192" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X192" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV192" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW192" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX192" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY192" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB192" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE192" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF192" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG192" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH192" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BI192" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ192" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK192" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BL192" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BM192" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN192" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO192" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BP192" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="n">
+        <v>8042777</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>46082.6875</v>
+      </c>
+      <c r="F193" t="n">
+        <v>20</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>National Bank of Egypt</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Smouha SC</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>1</v>
+      </c>
+      <c r="J193" t="n">
+        <v>2</v>
+      </c>
+      <c r="K193" t="n">
+        <v>3</v>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="n">
+        <v>3</v>
+      </c>
+      <c r="N193" t="n">
+        <v>4</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>['11', '40', '51']</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="R193" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S193" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="T193" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U193" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V193" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W193" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X193" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU193" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV193" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW193" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX193" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY193" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB193" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE193" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="BF193" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG193" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BH193" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI193" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BJ193" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BK193" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BL193" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BM193" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BN193" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO193" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="BP193" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="n">
+        <v>8042774</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>46082.6875</v>
+      </c>
+      <c r="F194" t="n">
+        <v>20</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Pyramids FC</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Zamalek</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>1</v>
+      </c>
+      <c r="N194" t="n">
+        <v>1</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R194" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S194" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="T194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U194" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V194" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W194" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X194" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV194" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW194" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX194" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY194" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB194" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC194" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE194" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BF194" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG194" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BH194" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BI194" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ194" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK194" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BL194" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BM194" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BN194" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BO194" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP194" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="n">
+        <v>8042776</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>46083.6875</v>
+      </c>
+      <c r="F195" t="n">
+        <v>20</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Pharco</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Kahraba Ismailia</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" t="n">
+        <v>1</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>2</v>
+      </c>
+      <c r="N195" t="n">
+        <v>2</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>['19', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R195" t="n">
+        <v>2</v>
+      </c>
+      <c r="S195" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T195" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U195" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V195" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W195" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X195" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AK195" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM195" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN195" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS195" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT195" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AU195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV195" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW195" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX195" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY195" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB195" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC195" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BE195" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF195" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BG195" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BH195" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BI195" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ195" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BK195" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BL195" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM195" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BN195" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BO195" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BP195" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>8042779</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>46083.6875</v>
+      </c>
+      <c r="F196" t="n">
+        <v>20</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Ghazl El Mehalla</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>2</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>2</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>['56', '88']</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R196" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S196" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="V196" t="n">
+        <v>4</v>
+      </c>
+      <c r="W196" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X196" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB196" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE196" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF196" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG196" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BH196" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BI196" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BL196" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BM196" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BN196" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BO196" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BP196" t="n">
         <v>1.17</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP196"/>
+  <dimension ref="A1:BP200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.11</v>
@@ -1568,7 +1568,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.4</v>
@@ -2222,7 +2222,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.5</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>1.09</v>
@@ -5928,7 +5928,7 @@
         <v>2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR25" t="n">
         <v>1.56</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.5</v>
@@ -7454,7 +7454,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR32" t="n">
         <v>1.08</v>
@@ -8108,7 +8108,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR35" t="n">
         <v>0.9</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.3</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.22</v>
@@ -9631,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.5</v>
@@ -9852,7 +9852,7 @@
         <v>1</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR43" t="n">
         <v>1.73</v>
@@ -10724,7 +10724,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR47" t="n">
         <v>1.47</v>
@@ -11811,10 +11811,10 @@
         <v>0.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR52" t="n">
         <v>1.71</v>
@@ -12683,7 +12683,7 @@
         <v>2</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.8</v>
@@ -12901,7 +12901,7 @@
         <v>2</v>
       </c>
       <c r="AP57" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.3</v>
@@ -13776,7 +13776,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR61" t="n">
         <v>1.03</v>
@@ -13991,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.67</v>
@@ -15520,7 +15520,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR69" t="n">
         <v>1.38</v>
@@ -16607,7 +16607,7 @@
         <v>1.25</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ74" t="n">
         <v>0.8</v>
@@ -16825,10 +16825,10 @@
         <v>1</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR75" t="n">
         <v>1.22</v>
@@ -17697,7 +17697,7 @@
         <v>2</v>
       </c>
       <c r="AP79" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ79" t="n">
         <v>1.38</v>
@@ -18351,7 +18351,7 @@
         <v>1.25</v>
       </c>
       <c r="AP82" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.5</v>
@@ -18572,7 +18572,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR83" t="n">
         <v>2.03</v>
@@ -19662,7 +19662,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR88" t="n">
         <v>0.97</v>
@@ -21406,7 +21406,7 @@
         <v>0.11</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR96" t="n">
         <v>1.12</v>
@@ -21621,7 +21621,7 @@
         <v>1.25</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.5</v>
@@ -22711,7 +22711,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ102" t="n">
         <v>1</v>
@@ -22932,7 +22932,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR103" t="n">
         <v>1.23</v>
@@ -23583,10 +23583,10 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR106" t="n">
         <v>1.22</v>
@@ -24455,7 +24455,7 @@
         <v>1.17</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.8</v>
@@ -25981,10 +25981,10 @@
         <v>1.8</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR117" t="n">
         <v>1.26</v>
@@ -27074,7 +27074,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR122" t="n">
         <v>1.79</v>
@@ -27507,7 +27507,7 @@
         <v>1.5</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ124" t="n">
         <v>1.1</v>
@@ -28161,7 +28161,7 @@
         <v>1.2</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.3</v>
@@ -28382,7 +28382,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR128" t="n">
         <v>1.49</v>
@@ -29036,7 +29036,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR131" t="n">
         <v>1.36</v>
@@ -29469,7 +29469,7 @@
         <v>0.83</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ133" t="n">
         <v>0.5</v>
@@ -30126,7 +30126,7 @@
         <v>0.11</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR136" t="n">
         <v>1.2</v>
@@ -30341,10 +30341,10 @@
         <v>2</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR137" t="n">
         <v>1.23</v>
@@ -30559,7 +30559,7 @@
         <v>0.67</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.78</v>
@@ -30995,7 +30995,7 @@
         <v>1.14</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ140" t="n">
         <v>1.5</v>
@@ -32742,7 +32742,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR148" t="n">
         <v>1.06</v>
@@ -33393,10 +33393,10 @@
         <v>1.71</v>
       </c>
       <c r="AP151" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR151" t="n">
         <v>1.5</v>
@@ -33832,7 +33832,7 @@
         <v>1</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR153" t="n">
         <v>1.48</v>
@@ -34050,7 +34050,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR154" t="n">
         <v>1.51</v>
@@ -34701,7 +34701,7 @@
         <v>0.71</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.67</v>
@@ -35137,7 +35137,7 @@
         <v>1</v>
       </c>
       <c r="AP159" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.8</v>
@@ -35791,7 +35791,7 @@
         <v>1.14</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ162" t="n">
         <v>1</v>
@@ -36230,7 +36230,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR164" t="n">
         <v>1.23</v>
@@ -37320,7 +37320,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR169" t="n">
         <v>1.17</v>
@@ -37535,7 +37535,7 @@
         <v>1.43</v>
       </c>
       <c r="AP170" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ170" t="n">
         <v>1.22</v>
@@ -39282,7 +39282,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AR178" t="n">
         <v>1.48</v>
@@ -39500,7 +39500,7 @@
         <v>0.11</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AR179" t="n">
         <v>1.2</v>
@@ -39718,7 +39718,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR180" t="n">
         <v>1</v>
@@ -39933,7 +39933,7 @@
         <v>1.13</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AQ181" t="n">
         <v>1</v>
@@ -40151,7 +40151,7 @@
         <v>0.38</v>
       </c>
       <c r="AP182" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.44</v>
@@ -41023,7 +41023,7 @@
         <v>0.88</v>
       </c>
       <c r="AP186" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AQ186" t="n">
         <v>0.78</v>
@@ -43227,13 +43227,13 @@
         <v>6</v>
       </c>
       <c r="AX196" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY196" t="n">
         <v>10</v>
       </c>
       <c r="AZ196" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA196" t="n">
         <v>2</v>
@@ -43282,6 +43282,878 @@
       </c>
       <c r="BP196" t="n">
         <v>1.17</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>8042780</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>46086.6875</v>
+      </c>
+      <c r="F197" t="n">
+        <v>21</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Petrojet</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>El Geish</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>2</v>
+      </c>
+      <c r="N197" t="n">
+        <v>3</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>['56', '82']</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R197" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S197" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U197" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V197" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W197" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X197" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE197" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF197" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BG197" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BH197" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI197" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ197" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BK197" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BM197" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BN197" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>8042781</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>46086.6875</v>
+      </c>
+      <c r="F198" t="n">
+        <v>21</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Pyramids FC</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" t="n">
+        <v>1</v>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="n">
+        <v>3</v>
+      </c>
+      <c r="N198" t="n">
+        <v>4</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>['42', '62', '87']</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>7</v>
+      </c>
+      <c r="R198" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S198" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U198" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V198" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X198" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF198" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BN198" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO198" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BP198" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>8042783</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>46086.6875</v>
+      </c>
+      <c r="F199" t="n">
+        <v>21</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>National Bank of Egypt</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" t="n">
+        <v>1</v>
+      </c>
+      <c r="L199" t="n">
+        <v>2</v>
+      </c>
+      <c r="M199" t="n">
+        <v>2</v>
+      </c>
+      <c r="N199" t="n">
+        <v>4</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>['56', '60']</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>['11', '76']</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R199" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S199" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V199" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X199" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BN199" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BO199" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="BP199" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>8042782</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>46086.6875</v>
+      </c>
+      <c r="F200" t="n">
+        <v>21</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Al Mokawloon</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Al Ahly</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="n">
+        <v>1</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="n">
+        <v>3</v>
+      </c>
+      <c r="N200" t="n">
+        <v>4</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>['35', '71', '90+5']</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R200" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S200" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U200" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V200" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="W200" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X200" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO200" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="BP200" t="n">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP200"/>
+  <dimension ref="A1:BP203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.3</v>
@@ -5710,7 +5710,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR24" t="n">
         <v>0.91</v>
@@ -5925,7 +5925,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ25" t="n">
         <v>2</v>
@@ -6579,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.8</v>
@@ -7890,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR34" t="n">
         <v>1.33</v>
@@ -8326,7 +8326,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR36" t="n">
         <v>0.93</v>
@@ -9413,7 +9413,7 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ41" t="n">
         <v>0.67</v>
@@ -10285,7 +10285,7 @@
         <v>2</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.4</v>
@@ -11157,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="AP49" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.5</v>
@@ -12032,7 +12032,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR53" t="n">
         <v>0.96</v>
@@ -12250,7 +12250,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR54" t="n">
         <v>0.93</v>
@@ -13119,7 +13119,7 @@
         <v>2</v>
       </c>
       <c r="AP58" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ58" t="n">
         <v>1.22</v>
@@ -13558,7 +13558,7 @@
         <v>0.11</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR60" t="n">
         <v>1.35</v>
@@ -14209,7 +14209,7 @@
         <v>1.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ63" t="n">
         <v>0.8</v>
@@ -14427,7 +14427,7 @@
         <v>1.67</v>
       </c>
       <c r="AP64" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.1</v>
@@ -16392,7 +16392,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR73" t="n">
         <v>1.07</v>
@@ -17043,7 +17043,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.8</v>
@@ -17482,7 +17482,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR78" t="n">
         <v>0.97</v>
@@ -17918,7 +17918,7 @@
         <v>1</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR80" t="n">
         <v>1.86</v>
@@ -18787,7 +18787,7 @@
         <v>1.5</v>
       </c>
       <c r="AP84" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.1</v>
@@ -19877,7 +19877,7 @@
         <v>1.33</v>
       </c>
       <c r="AP89" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ89" t="n">
         <v>1.5</v>
@@ -20316,7 +20316,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR91" t="n">
         <v>1.51</v>
@@ -21185,7 +21185,7 @@
         <v>1.2</v>
       </c>
       <c r="AP95" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ95" t="n">
         <v>0.8</v>
@@ -22060,7 +22060,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR99" t="n">
         <v>1.02</v>
@@ -22929,7 +22929,7 @@
         <v>1.75</v>
       </c>
       <c r="AP103" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.7</v>
@@ -24022,7 +24022,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR108" t="n">
         <v>1.65</v>
@@ -24237,7 +24237,7 @@
         <v>1.25</v>
       </c>
       <c r="AP109" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ109" t="n">
         <v>1.3</v>
@@ -25112,7 +25112,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR113" t="n">
         <v>1.08</v>
@@ -25766,7 +25766,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR116" t="n">
         <v>1.25</v>
@@ -26853,7 +26853,7 @@
         <v>0.4</v>
       </c>
       <c r="AP121" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.67</v>
@@ -27071,7 +27071,7 @@
         <v>0.83</v>
       </c>
       <c r="AP122" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ122" t="n">
         <v>1</v>
@@ -27292,7 +27292,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR123" t="n">
         <v>1.97</v>
@@ -30562,7 +30562,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR138" t="n">
         <v>1.27</v>
@@ -31652,7 +31652,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR143" t="n">
         <v>1.76</v>
@@ -31867,7 +31867,7 @@
         <v>1.29</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.1</v>
@@ -32303,7 +32303,7 @@
         <v>2</v>
       </c>
       <c r="AP146" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ146" t="n">
         <v>1.5</v>
@@ -32960,7 +32960,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR149" t="n">
         <v>1.29</v>
@@ -35355,7 +35355,7 @@
         <v>1.67</v>
       </c>
       <c r="AP160" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.38</v>
@@ -35576,7 +35576,7 @@
         <v>1</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR161" t="n">
         <v>1.46</v>
@@ -36012,7 +36012,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR163" t="n">
         <v>1.83</v>
@@ -36445,7 +36445,7 @@
         <v>1.43</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ165" t="n">
         <v>1.3</v>
@@ -36663,10 +36663,10 @@
         <v>1.57</v>
       </c>
       <c r="AP166" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR166" t="n">
         <v>1.31</v>
@@ -38407,7 +38407,7 @@
         <v>0.63</v>
       </c>
       <c r="AP174" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.5</v>
@@ -38628,7 +38628,7 @@
         <v>0.7</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AR175" t="n">
         <v>1.09</v>
@@ -39061,7 +39061,7 @@
         <v>1.33</v>
       </c>
       <c r="AP177" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.3</v>
@@ -40154,7 +40154,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ182" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR182" t="n">
         <v>1.38</v>
@@ -40805,7 +40805,7 @@
         <v>1.57</v>
       </c>
       <c r="AP185" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ185" t="n">
         <v>1.38</v>
@@ -41026,7 +41026,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ186" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR186" t="n">
         <v>1.18</v>
@@ -43457,10 +43457,10 @@
         <v>1</v>
       </c>
       <c r="BB197" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC197" t="n">
         <v>6</v>
-      </c>
-      <c r="BC197" t="n">
-        <v>7</v>
       </c>
       <c r="BD197" t="n">
         <v>1.78</v>
@@ -43657,13 +43657,13 @@
         <v>3</v>
       </c>
       <c r="AV198" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW198" t="n">
         <v>5</v>
       </c>
       <c r="AX198" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY198" t="n">
         <v>8</v>
@@ -44154,6 +44154,660 @@
       </c>
       <c r="BP200" t="n">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>8042786</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>46087.6875</v>
+      </c>
+      <c r="F201" t="n">
+        <v>21</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Zamalek</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>1</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>1</v>
+      </c>
+      <c r="L201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>1</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>['11']</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R201" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S201" t="n">
+        <v>7</v>
+      </c>
+      <c r="T201" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U201" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V201" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X201" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP201" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>8042785</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>46087.6875</v>
+      </c>
+      <c r="F202" t="n">
+        <v>21</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>El Gounah</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Wadi Degla</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R202" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S202" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T202" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U202" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V202" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="W202" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X202" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>8042784</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>46087.6875</v>
+      </c>
+      <c r="F203" t="n">
+        <v>21</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Al Masry</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Ismaily SC</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>1</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>1</v>
+      </c>
+      <c r="L203" t="n">
+        <v>2</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>2</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>['45+3', '90+6']</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R203" t="n">
+        <v>2</v>
+      </c>
+      <c r="S203" t="n">
+        <v>6</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U203" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V203" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="W203" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X203" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP203"/>
+  <dimension ref="A1:BP206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.8</v>
@@ -2658,7 +2658,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.3</v>
@@ -6146,7 +6146,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR26" t="n">
         <v>0.7</v>
@@ -7233,7 +7233,7 @@
         <v>3</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.4</v>
@@ -8105,7 +8105,7 @@
         <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.89</v>
@@ -8762,7 +8762,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR38" t="n">
         <v>2.18</v>
@@ -8977,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.3</v>
@@ -9416,7 +9416,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR41" t="n">
         <v>1.07</v>
@@ -10070,7 +10070,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR44" t="n">
         <v>1.07</v>
@@ -11375,7 +11375,7 @@
         <v>2</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.1</v>
@@ -12465,7 +12465,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.3</v>
@@ -13340,7 +13340,7 @@
         <v>1</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR59" t="n">
         <v>1.3</v>
@@ -13555,7 +13555,7 @@
         <v>1.5</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.6</v>
@@ -13994,7 +13994,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR62" t="n">
         <v>1.86</v>
@@ -14866,7 +14866,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR66" t="n">
         <v>1.1</v>
@@ -15735,7 +15735,7 @@
         <v>0.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.5</v>
@@ -17700,7 +17700,7 @@
         <v>2.3</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR79" t="n">
         <v>1.07</v>
@@ -19008,7 +19008,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR85" t="n">
         <v>1.32</v>
@@ -19441,10 +19441,10 @@
         <v>1.25</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR87" t="n">
         <v>0.96</v>
@@ -20313,7 +20313,7 @@
         <v>0.75</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.4</v>
@@ -21403,7 +21403,7 @@
         <v>1.5</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AQ96" t="n">
         <v>1.89</v>
@@ -22278,7 +22278,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR100" t="n">
         <v>1.21</v>
@@ -22493,7 +22493,7 @@
         <v>1.6</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ101" t="n">
         <v>1.5</v>
@@ -22714,7 +22714,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR102" t="n">
         <v>1.61</v>
@@ -23804,7 +23804,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR107" t="n">
         <v>1.92</v>
@@ -24891,7 +24891,7 @@
         <v>1.6</v>
       </c>
       <c r="AP112" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.5</v>
@@ -25545,7 +25545,7 @@
         <v>1.6</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.8</v>
@@ -26417,10 +26417,10 @@
         <v>1.8</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR119" t="n">
         <v>1.13</v>
@@ -26856,7 +26856,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR121" t="n">
         <v>1.23</v>
@@ -28818,7 +28818,7 @@
         <v>1</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR130" t="n">
         <v>1.31</v>
@@ -29687,7 +29687,7 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AQ134" t="n">
         <v>1.4</v>
@@ -30123,7 +30123,7 @@
         <v>1.67</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AQ136" t="n">
         <v>2</v>
@@ -30777,10 +30777,10 @@
         <v>0.83</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR139" t="n">
         <v>1.5</v>
@@ -32739,7 +32739,7 @@
         <v>0.71</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ148" t="n">
         <v>1</v>
@@ -34047,7 +34047,7 @@
         <v>1.8</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ154" t="n">
         <v>2</v>
@@ -34483,7 +34483,7 @@
         <v>1.67</v>
       </c>
       <c r="AP156" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AQ156" t="n">
         <v>2.11</v>
@@ -34704,7 +34704,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR157" t="n">
         <v>1.2</v>
@@ -35358,7 +35358,7 @@
         <v>0.78</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR160" t="n">
         <v>1.22</v>
@@ -35794,7 +35794,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR162" t="n">
         <v>1.17</v>
@@ -38843,7 +38843,7 @@
         <v>1.5</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.4</v>
@@ -39279,7 +39279,7 @@
         <v>1.57</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.89</v>
@@ -39497,7 +39497,7 @@
         <v>0.75</v>
       </c>
       <c r="AP179" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AQ179" t="n">
         <v>1</v>
@@ -39715,7 +39715,7 @@
         <v>1.71</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ180" t="n">
         <v>2</v>
@@ -39936,7 +39936,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR181" t="n">
         <v>1.25</v>
@@ -40590,7 +40590,7 @@
         <v>1</v>
       </c>
       <c r="AQ184" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR184" t="n">
         <v>1.38</v>
@@ -40808,7 +40808,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR185" t="n">
         <v>1.31</v>
@@ -44808,6 +44808,660 @@
       </c>
       <c r="BP203" t="n">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>8042788</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>46088.6875</v>
+      </c>
+      <c r="F204" t="n">
+        <v>21</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Ghazl El Mehalla</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Pharco</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R204" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="S204" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V204" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X204" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>8042787</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>46088.6875</v>
+      </c>
+      <c r="F205" t="n">
+        <v>21</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Kahraba Ismailia</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>ENPPI</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="n">
+        <v>1</v>
+      </c>
+      <c r="L205" t="n">
+        <v>1</v>
+      </c>
+      <c r="M205" t="n">
+        <v>2</v>
+      </c>
+      <c r="N205" t="n">
+        <v>3</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>['15', '87']</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R205" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S205" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V205" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X205" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP205" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>8042789</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>46088.6875</v>
+      </c>
+      <c r="F206" t="n">
+        <v>21</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Smouha SC</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>2</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>2</v>
+      </c>
+      <c r="L206" t="n">
+        <v>3</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>3</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>['22', '36', '53']</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R206" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S206" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U206" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V206" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X206" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BO206" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP206" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Egypt Egyptian Premier League_20252026.xlsx
@@ -44971,13 +44971,13 @@
         <v>8</v>
       </c>
       <c r="AX204" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY204" t="n">
         <v>10</v>
       </c>
       <c r="AZ204" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA204" t="n">
         <v>2</v>
